--- a/BOM/JLCPCB-BOM.xlsx
+++ b/BOM/JLCPCB-BOM.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="182">
   <si>
     <t>Comment</t>
   </si>
@@ -60,16 +60,13 @@
     <t>8.2nF</t>
   </si>
   <si>
-    <t>PESD5V0H1BSFYL</t>
-  </si>
-  <si>
     <t>ESD5302F-3/TR</t>
   </si>
   <si>
     <t>DSK24 K24</t>
   </si>
   <si>
-    <t>BSMD0805L-200</t>
+    <t>SS32 /SMA(DO-214AC)</t>
   </si>
   <si>
     <t>BLM18SG121TN1D</t>
@@ -78,10 +75,10 @@
     <t>BLM18PG181SN1D</t>
   </si>
   <si>
-    <t>TYPE-C-31-M-12</t>
-  </si>
-  <si>
-    <t>B2B-XH-A(LF)(SN)</t>
+    <t>POGO Connector 4 Pin</t>
+  </si>
+  <si>
+    <t>1.25-2PWB</t>
   </si>
   <si>
     <t>DM3BT-DSF-PEJS</t>
@@ -90,7 +87,7 @@
     <t>FH12A-40S-0.5SH(55)</t>
   </si>
   <si>
-    <t>B3B-XH-A(LF)(SN)</t>
+    <t>1.25-5PWB</t>
   </si>
   <si>
     <t>2.2uH</t>
@@ -105,13 +102,10 @@
     <t>10K</t>
   </si>
   <si>
-    <t>5.1K</t>
-  </si>
-  <si>
     <t>0R</t>
   </si>
   <si>
-    <t>1.2K</t>
+    <t>1.5K</t>
   </si>
   <si>
     <t>4.7K</t>
@@ -141,18 +135,12 @@
     <t>270K</t>
   </si>
   <si>
-    <t>33K</t>
-  </si>
-  <si>
-    <t>8.2K</t>
-  </si>
-  <si>
-    <t>3.3K</t>
-  </si>
-  <si>
     <t>B3U-1000P</t>
   </si>
   <si>
+    <t>DSIC01LSGET</t>
+  </si>
+  <si>
     <t>SS-12D02-G040</t>
   </si>
   <si>
@@ -204,7 +192,7 @@
     <t>C5</t>
   </si>
   <si>
-    <t>C9, C11, C15, C17, C19, C20, C21, C22, C25, C26, C31, C37, C39, C40, C42, C45, C47, C49, C54, C59, C60, C61, C62, C63, C64</t>
+    <t>C9, C11, C15, C17, C19, C20, C21, C22, C25, C26, C31, C37, C39, C40, C42, C45, C47, C49, C54, C59, C60, C61</t>
   </si>
   <si>
     <t>C14, C52</t>
@@ -231,16 +219,13 @@
     <t>C58</t>
   </si>
   <si>
-    <t>D1</t>
-  </si>
-  <si>
     <t>D2</t>
   </si>
   <si>
     <t>D3</t>
   </si>
   <si>
-    <t>F1</t>
+    <t>D4</t>
   </si>
   <si>
     <t>FB1, FB2</t>
@@ -252,7 +237,7 @@
     <t>J1</t>
   </si>
   <si>
-    <t>J2, J6</t>
+    <t>J2, J5, J6</t>
   </si>
   <si>
     <t>J3</t>
@@ -261,7 +246,7 @@
     <t>J4</t>
   </si>
   <si>
-    <t>J5</t>
+    <t>J7</t>
   </si>
   <si>
     <t>L1</t>
@@ -273,7 +258,7 @@
     <t>Q2</t>
   </si>
   <si>
-    <t>R2, R3, R37</t>
+    <t>R1, R2, R6, R7, R8, R9, R10, R13, R14, R15, R31, R32</t>
   </si>
   <si>
     <t>R4, R22, R23</t>
@@ -309,16 +294,10 @@
     <t>R35</t>
   </si>
   <si>
-    <t>R38</t>
-  </si>
-  <si>
-    <t>R39</t>
-  </si>
-  <si>
-    <t>R40</t>
-  </si>
-  <si>
-    <t>SW1, SW2, SW3, SW4, SW5</t>
+    <t>SW1, SW2</t>
+  </si>
+  <si>
+    <t>SW3</t>
   </si>
   <si>
     <t>SW6</t>
@@ -372,28 +351,19 @@
     <t>Cap-0805</t>
   </si>
   <si>
-    <t>DSN0603-2</t>
-  </si>
-  <si>
     <t>Sot-23</t>
   </si>
   <si>
     <t>SOD-123FL</t>
   </si>
   <si>
-    <t>Fuse-0805</t>
+    <t>SMA</t>
   </si>
   <si>
     <t>IND-0603 (1608 Metric)</t>
   </si>
   <si>
-    <t>TYPE-C-31-M-12_</t>
-  </si>
-  <si>
-    <t>B2B-XH-A(LF)(SN)_</t>
-  </si>
-  <si>
-    <t>B3B-XH-A(LF)(SN)_</t>
+    <t>Pogo 4 Pin</t>
   </si>
   <si>
     <t>IHHP0806AZER2R2M01</t>
@@ -483,16 +453,13 @@
     <t>C113812</t>
   </si>
   <si>
-    <t>C477989</t>
-  </si>
-  <si>
     <t>C239643</t>
   </si>
   <si>
     <t>C64890</t>
   </si>
   <si>
-    <t>C2757931</t>
+    <t>C34897</t>
   </si>
   <si>
     <t>C113030</t>
@@ -501,16 +468,13 @@
     <t>C82850</t>
   </si>
   <si>
-    <t>C165948</t>
-  </si>
-  <si>
-    <t>C158012</t>
+    <t>C2905009</t>
   </si>
   <si>
     <t>C597972</t>
   </si>
   <si>
-    <t>C144394</t>
+    <t>C2905012</t>
   </si>
   <si>
     <t>C1330968</t>
@@ -525,10 +489,7 @@
     <t>C98220</t>
   </si>
   <si>
-    <t>C105580</t>
-  </si>
-  <si>
-    <t>C114605</t>
+    <t>C114668</t>
   </si>
   <si>
     <t>C105428</t>
@@ -558,18 +519,12 @@
     <t>C724006</t>
   </si>
   <si>
-    <t>C705768</t>
-  </si>
-  <si>
-    <t>C861589</t>
-  </si>
-  <si>
-    <t>C108078</t>
-  </si>
-  <si>
     <t>C231329</t>
   </si>
   <si>
+    <t>C54948</t>
+  </si>
+  <si>
     <t>C2876023</t>
   </si>
   <si>
@@ -603,16 +558,13 @@
     <t>C129522</t>
   </si>
   <si>
-    <t>R1, R6, R7, R8, R10, R13, R14, R15, R31, R32</t>
+    <t>C15651</t>
   </si>
   <si>
     <t>C95177</t>
   </si>
   <si>
     <t>C506795</t>
-  </si>
-  <si>
-    <t>C15651</t>
   </si>
 </sst>
 </file>
@@ -1058,7 +1010,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -1072,13 +1024,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -1086,13 +1038,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1100,13 +1052,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="24" x14ac:dyDescent="0.25">
@@ -1114,13 +1066,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1128,13 +1080,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="36" x14ac:dyDescent="0.25">
@@ -1142,13 +1094,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1156,13 +1108,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1170,13 +1122,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1184,13 +1136,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1198,13 +1150,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1212,13 +1164,13 @@
         <v>6</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1226,13 +1178,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1240,13 +1192,13 @@
         <v>11</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1254,13 +1206,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1268,13 +1220,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1282,13 +1234,13 @@
         <v>14</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1296,13 +1248,13 @@
         <v>15</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1310,13 +1262,13 @@
         <v>16</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1324,13 +1276,13 @@
         <v>17</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1338,27 +1290,25 @@
         <v>18</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>159</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="D20" s="4"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>122</v>
+        <v>19</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1366,13 +1316,13 @@
         <v>20</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>123</v>
+        <v>20</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1380,13 +1330,13 @@
         <v>21</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>162</v>
+        <v>181</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1394,13 +1344,13 @@
         <v>22</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D24" s="6" t="s">
-        <v>196</v>
+      <c r="D24" s="4" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1408,27 +1358,27 @@
         <v>23</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>164</v>
+      <c r="B26" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1436,27 +1386,27 @@
         <v>25</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="24" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1464,13 +1414,13 @@
         <v>27</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>194</v>
+        <v>80</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>167</v>
+        <v>117</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1478,13 +1428,13 @@
         <v>28</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1492,13 +1442,13 @@
         <v>29</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>195</v>
+        <v>117</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1506,13 +1456,13 @@
         <v>30</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1520,13 +1470,13 @@
         <v>31</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1534,13 +1484,13 @@
         <v>32</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1548,13 +1498,13 @@
         <v>33</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1562,13 +1512,13 @@
         <v>34</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1576,13 +1526,13 @@
         <v>35</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1590,13 +1540,13 @@
         <v>36</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1604,13 +1554,13 @@
         <v>37</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1618,13 +1568,13 @@
         <v>38</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>127</v>
+        <v>38</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1632,13 +1582,13 @@
         <v>39</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>127</v>
+        <v>39</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1646,13 +1596,13 @@
         <v>40</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>127</v>
+        <v>40</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1660,13 +1610,13 @@
         <v>41</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1674,195 +1624,139 @@
         <v>42</v>
       </c>
       <c r="B44" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B47" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="C44" s="7" t="s">
+      <c r="C47" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="24" x14ac:dyDescent="0.25">
+      <c r="A48" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C51" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="D44" s="6" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D45" s="6" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C47" s="7" t="s">
+      <c r="D51" s="4" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C53" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="D47" s="6" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="D49" s="6" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="D51" s="6" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" ht="24" x14ac:dyDescent="0.25">
-      <c r="A52" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="D53" s="6" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="D55" s="6" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="C56" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="D57" s="6" t="s">
-        <v>193</v>
+      <c r="D53" s="4" t="s">
+        <v>178</v>
       </c>
     </row>
   </sheetData>

--- a/BOM/JLCPCB-BOM.xlsx
+++ b/BOM/JLCPCB-BOM.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="179">
   <si>
     <t>Comment</t>
   </si>
@@ -75,9 +75,6 @@
     <t>BLM18PG181SN1D</t>
   </si>
   <si>
-    <t>POGO Connector 4 Pin</t>
-  </si>
-  <si>
     <t>1.25-2PWB</t>
   </si>
   <si>
@@ -234,9 +231,6 @@
     <t>FB3</t>
   </si>
   <si>
-    <t>J1</t>
-  </si>
-  <si>
     <t>J2, J5, J6</t>
   </si>
   <si>
@@ -363,9 +357,6 @@
     <t>IND-0603 (1608 Metric)</t>
   </si>
   <si>
-    <t>Pogo 4 Pin</t>
-  </si>
-  <si>
     <t>IHHP0806AZER2R2M01</t>
   </si>
   <si>
@@ -429,18 +420,12 @@
     <t>C106256</t>
   </si>
   <si>
-    <t>C2936601</t>
-  </si>
-  <si>
     <t>C338080</t>
   </si>
   <si>
     <t>C277476</t>
   </si>
   <si>
-    <t>C441758</t>
-  </si>
-  <si>
     <t>C326057</t>
   </si>
   <si>
@@ -565,6 +550,12 @@
   </si>
   <si>
     <t>C506795</t>
+  </si>
+  <si>
+    <t>C92487</t>
+  </si>
+  <si>
+    <t>C881842</t>
   </si>
 </sst>
 </file>
@@ -1010,7 +1001,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -1024,13 +1015,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -1038,13 +1029,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1052,13 +1043,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="24" x14ac:dyDescent="0.25">
@@ -1066,13 +1057,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1080,13 +1071,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="36" x14ac:dyDescent="0.25">
@@ -1094,13 +1085,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1108,13 +1099,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>136</v>
+        <v>177</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1122,13 +1113,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1136,13 +1127,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1150,13 +1141,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>139</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1164,13 +1155,13 @@
         <v>6</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1178,13 +1169,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>141</v>
+        <v>104</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1192,13 +1183,13 @@
         <v>11</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>142</v>
+        <v>104</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1206,13 +1197,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>143</v>
+        <v>104</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1220,13 +1211,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1234,13 +1225,13 @@
         <v>14</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1248,13 +1239,13 @@
         <v>15</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1262,13 +1253,13 @@
         <v>16</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1276,81 +1267,83 @@
         <v>17</v>
       </c>
       <c r="B19" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C19" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
+      <c r="C20" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="D20" s="6" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C20" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="D20" s="4"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
+      <c r="C21" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="D21" s="4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="C21" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
+      <c r="C22" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="D22" s="6" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="s">
+      <c r="C23" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="D23" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="C23" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>151</v>
+      <c r="C24" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1358,405 +1351,391 @@
         <v>23</v>
       </c>
       <c r="B25" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C26" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="24" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C31" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="D25" s="6" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C26" s="7" t="s">
+      <c r="D31" s="6" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C42" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="D26" s="6" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="24" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C28" s="7" t="s">
+      <c r="D42" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C43" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="D28" s="6" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C32" s="7" t="s">
+      <c r="D43" s="6" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C44" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="D32" s="6" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="D39" s="4" t="s">
+      <c r="D44" s="4" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D40" s="6" t="s">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D45" s="6" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D41" s="4" t="s">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D46" s="4" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D42" s="6" t="s">
+    <row r="47" spans="1:4" ht="24" x14ac:dyDescent="0.25">
+      <c r="A47" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="D47" s="6" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="D43" s="4" t="s">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D48" s="4" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="C44" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="D45" s="4" t="s">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="D49" s="6" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="D46" s="6" t="s">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="D50" s="4" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="D47" s="4" t="s">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="D51" s="6" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="24" x14ac:dyDescent="0.25">
-      <c r="A48" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="D48" s="6" t="s">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="D52" s="4" t="s">
         <v>173</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="D50" s="6" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="D52" s="6" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>178</v>
       </c>
     </row>
   </sheetData>

--- a/BOM/JLCPCB-BOM.xlsx
+++ b/BOM/JLCPCB-BOM.xlsx
@@ -132,7 +132,7 @@
     <t>270K</t>
   </si>
   <si>
-    <t>B3U-1000P</t>
+    <t>TS-1109S-C-B</t>
   </si>
   <si>
     <t>DSIC01LSGET</t>
@@ -420,12 +420,18 @@
     <t>C106256</t>
   </si>
   <si>
+    <t>C2936601</t>
+  </si>
+  <si>
     <t>C338080</t>
   </si>
   <si>
     <t>C277476</t>
   </si>
   <si>
+    <t>C441758</t>
+  </si>
+  <si>
     <t>C326057</t>
   </si>
   <si>
@@ -480,9 +486,6 @@
     <t>C105428</t>
   </si>
   <si>
-    <t>C137211</t>
-  </si>
-  <si>
     <t>C107701</t>
   </si>
   <si>
@@ -504,7 +507,7 @@
     <t>C724006</t>
   </si>
   <si>
-    <t>C231329</t>
+    <t>C381037</t>
   </si>
   <si>
     <t>C54948</t>
@@ -543,19 +546,16 @@
     <t>C129522</t>
   </si>
   <si>
+    <t>C506795</t>
+  </si>
+  <si>
+    <t>C95177</t>
+  </si>
+  <si>
     <t>C15651</t>
   </si>
   <si>
-    <t>C95177</t>
-  </si>
-  <si>
-    <t>C506795</t>
-  </si>
-  <si>
-    <t>C92487</t>
-  </si>
-  <si>
-    <t>C881842</t>
+    <t>C431873</t>
   </si>
 </sst>
 </file>
@@ -1105,7 +1105,7 @@
         <v>104</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>177</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1119,7 +1119,7 @@
         <v>107</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1133,7 +1133,7 @@
         <v>104</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1147,7 +1147,7 @@
         <v>106</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>178</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1161,7 +1161,7 @@
         <v>104</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1174,8 +1174,8 @@
       <c r="C12" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>136</v>
+      <c r="D12" s="4" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1188,8 +1188,8 @@
       <c r="C13" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>137</v>
+      <c r="D13" s="6" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1202,8 +1202,8 @@
       <c r="C14" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="D14" s="6" t="s">
-        <v>138</v>
+      <c r="D14" s="4" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1217,7 +1217,7 @@
         <v>108</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1231,7 +1231,7 @@
         <v>109</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1245,7 +1245,7 @@
         <v>110</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1259,7 +1259,7 @@
         <v>111</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1273,7 +1273,7 @@
         <v>111</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1287,7 +1287,7 @@
         <v>18</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1301,7 +1301,7 @@
         <v>19</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1315,7 +1315,7 @@
         <v>20</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1329,7 +1329,7 @@
         <v>21</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1343,7 +1343,7 @@
         <v>112</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1357,7 +1357,7 @@
         <v>113</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1371,7 +1371,7 @@
         <v>113</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="24" x14ac:dyDescent="0.25">
@@ -1385,7 +1385,7 @@
         <v>114</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1399,7 +1399,7 @@
         <v>114</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1413,7 +1413,7 @@
         <v>114</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1427,7 +1427,7 @@
         <v>114</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1441,7 +1441,7 @@
         <v>115</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>153</v>
+        <v>178</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1455,7 +1455,7 @@
         <v>114</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1469,7 +1469,7 @@
         <v>114</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1483,7 +1483,7 @@
         <v>114</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1497,7 +1497,7 @@
         <v>114</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1511,7 +1511,7 @@
         <v>114</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1525,7 +1525,7 @@
         <v>114</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1539,7 +1539,7 @@
         <v>114</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1553,7 +1553,7 @@
         <v>37</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1567,7 +1567,7 @@
         <v>38</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1581,7 +1581,7 @@
         <v>39</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1595,7 +1595,7 @@
         <v>116</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1609,7 +1609,7 @@
         <v>117</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1623,7 +1623,7 @@
         <v>118</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1637,7 +1637,7 @@
         <v>119</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1651,7 +1651,7 @@
         <v>120</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="24" x14ac:dyDescent="0.25">
@@ -1665,7 +1665,7 @@
         <v>121</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -1679,7 +1679,7 @@
         <v>122</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -1693,7 +1693,7 @@
         <v>123</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -1707,7 +1707,7 @@
         <v>124</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -1721,7 +1721,7 @@
         <v>125</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -1735,7 +1735,7 @@
         <v>126</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
